--- a/survey_templates/031_wi_fi_settings_survey--survey_templates.xlsx
+++ b/survey_templates/031_wi_fi_settings_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,20 +515,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>page1</t>
+          <t>current_provider</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wi-Fi Settings</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is your current Wi-Fi network provider?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please select your current provider.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -538,20 +542,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>page2</t>
+          <t>devices_connected</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wi-Fi</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>How many devices are connected to your Wi-Fi network?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please count the number of devices connected to your network.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -561,20 +569,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>page3</t>
+          <t>preferred_speed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wi-Fi Settings</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>What is your preferred Wi-Fi speed?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Select your preferred speed.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -584,20 +596,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>page4</t>
+          <t>streaming_frequency</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Page 4</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>How often do you use your Wi-Fi for streaming?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Select how often you stream.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -607,20 +623,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>page5</t>
+          <t>connection_issues</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wi-Fi Settings</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Do you have any issues with your current Wi-Fi connection?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Check the box if you have issues.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -630,20 +650,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>page6</t>
+          <t>devices_at_home</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Page 6</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>How many devices do you typically use on your Wi-Fi network at home?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please count the devices.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -653,20 +677,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>page7</t>
+          <t>monthly_data</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Page 7</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>How much data do you use per month on your Wi-Fi network?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Estimate your monthly data usage.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -681,15 +709,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>page8</t>
+          <t>router_or_access_point</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wi-Fi Settings</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Do you use a router or access point for your Wi-Fi?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Check the box if you use a router.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -699,20 +731,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>page9</t>
+          <t>internet_plan_speed</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Page 9</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>What is your current internet plan speed?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please select your speed.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -727,15 +763,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>page10</t>
+          <t>users_at_network</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Page 10</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>How many users are connected to your Wi-Fi network?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Estimate the number of users.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -745,20 +785,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>page11</t>
+          <t>wifi_issues_at_home_work</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Page 11</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Do you have any Wi-Fi-related issues at home or work?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Check the box if you have issues.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -768,320 +812,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>page12</t>
+          <t>plan_to_increase_speed</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Page 12</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Do you plan to increase your Wi-Fi speed in the next 6 months?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Check the box if you plan to increase speed.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>page13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Page 13</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>page14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Page 14</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>page15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Page 15</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>page16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Page 16</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>page17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Page 17</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>page18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Page 18</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>page19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Page 19</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>page20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Page 20</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>page21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Page 21</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>page22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Page 22</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>page23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Page 23</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>page24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Page 24</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>page25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Page 25</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +847,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,408 +875,255 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>page2_choices</t>
+          <t>current_provider_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>verizon</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Verizon</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>page2_choices</t>
+          <t>current_provider_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>at&amp;t</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>page2_choices</t>
+          <t>current_provider_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>t-mobile</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>T-Mobile</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>page5_choices</t>
+          <t>current_provider_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>page5_choices</t>
+          <t>preferred_speed_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>low_(1-10_mbps)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Low (1-10 Mbps)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>page5_choices</t>
+          <t>preferred_speed_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>medium_(11-50_mbps)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Medium (11-50 Mbps)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>page11_choices</t>
+          <t>preferred_speed_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>high_(51-100_mbps)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>High (51-100 Mbps)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>page11_choices</t>
+          <t>preferred_speed_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>very_high_(100+_mbps)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Very High (100+ Mbps)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>page11_choices</t>
+          <t>streaming_frequency_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>page12_choices</t>
+          <t>streaming_frequency_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>page12_choices</t>
+          <t>streaming_frequency_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>page12_choices</t>
+          <t>internet_plan_speed_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>low_(1-5_mbps)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Low (1-5 Mbps)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>page17_choices</t>
+          <t>internet_plan_speed_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>medium_(6-20_mbps)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Medium (6-20 Mbps)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>page17_choices</t>
+          <t>internet_plan_speed_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>high_(21-50_mbps)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>High (21-50 Mbps)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>page17_choices</t>
+          <t>internet_plan_speed_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>very_high_(51+_mbps)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>page19_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>page19_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>page19_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>page23_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>page23_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>page23_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>page25_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>page25_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>page25_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Option 3</t>
+          <t>Very High (51+ Mbps)</t>
         </is>
       </c>
     </row>
